--- a/data/trans_orig/IP22-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102796</t>
+          <t>102442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117667</t>
+          <t>118124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119999</t>
+          <t>118792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134540</t>
+          <t>133750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228248</t>
+          <t>227891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249395</t>
+          <t>249110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>34285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>42693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63555</t>
+          <t>63912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147112</t>
+          <t>146415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163887</t>
+          <t>163470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144542</t>
+          <t>146202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165435</t>
+          <t>165925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295924</t>
+          <t>296806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323100</t>
+          <t>324583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65741</t>
+          <t>63881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82508</t>
+          <t>80467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109550</t>
+          <t>108326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93028</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109081</t>
+          <t>108670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100369</t>
+          <t>101676</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118116</t>
+          <t>118298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>199557</t>
+          <t>199159</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>224242</t>
+          <t>223428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27335</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>44173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47857</t>
+          <t>46884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>62117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84850</t>
+          <t>85867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171490</t>
+          <t>172543</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189264</t>
+          <t>189411</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163220</t>
+          <t>163421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180485</t>
+          <t>181042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340933</t>
+          <t>341664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364730</t>
+          <t>366832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>44403</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52409</t>
+          <t>50307</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76206</t>
+          <t>75475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>532737</t>
+          <t>532651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>566201</t>
+          <t>566210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>547412</t>
+          <t>547601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582857</t>
+          <t>582686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1091840</t>
+          <t>1088057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1139182</t>
+          <t>1139560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114159</t>
+          <t>113439</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>147599</t>
+          <t>147250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137001</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172167</t>
+          <t>171199</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260816</t>
+          <t>259608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307581</t>
+          <t>310094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98773</t>
+          <t>97401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114920</t>
+          <t>114958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105715</t>
+          <t>106592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125715</t>
+          <t>125190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210849</t>
+          <t>210029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235942</t>
+          <t>235328</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23635</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28969</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>48092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>58011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83202</t>
+          <t>83291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135252</t>
+          <t>134974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155653</t>
+          <t>156067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150109</t>
+          <t>150697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172043</t>
+          <t>173194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291934</t>
+          <t>292033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323286</t>
+          <t>323000</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50060</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70461</t>
+          <t>70739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47079</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68642</t>
+          <t>68250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101283</t>
+          <t>101824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130805</t>
+          <t>132231</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113792</t>
+          <t>114747</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130353</t>
+          <t>130436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>93738</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113684</t>
+          <t>114018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>212927</t>
+          <t>212935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>239531</t>
+          <t>237962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41101</t>
+          <t>39953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50464</t>
+          <t>50735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70872</t>
+          <t>70740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>79758</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106218</t>
+          <t>106014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157820</t>
+          <t>156683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177787</t>
+          <t>176912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152008</t>
+          <t>150786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171108</t>
+          <t>171603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>313726</t>
+          <t>314938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344306</t>
+          <t>343739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>30566</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,82 +4854,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>44339</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>34708</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>55173</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>83966</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>70455</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>97892</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>23,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44339</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>34855</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54508</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>21,35%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>83966</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>69856</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>99810</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>523584</t>
+          <t>523740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>521519</t>
+          <t>522517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>563002</t>
+          <t>563418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1056984</t>
+          <t>1057381</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1114274</t>
+          <t>1112764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145830</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183558</t>
+          <t>182195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181402</t>
+          <t>181662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222058</t>
+          <t>221723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336866</t>
+          <t>338655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>393635</t>
+          <t>393261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>98771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114342</t>
+          <t>113940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112869</t>
+          <t>112034</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>129487</t>
+          <t>129500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216580</t>
+          <t>216350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>239657</t>
+          <t>238673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>526</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34367</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>41386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63046</t>
+          <t>62794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159510</t>
+          <t>159249</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177039</t>
+          <t>176918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179789</t>
+          <t>179598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>197950</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344497</t>
+          <t>343907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369074</t>
+          <t>369310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44811</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25386</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43198</t>
+          <t>43504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,47 +6489,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>69565</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>58487</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>83098</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>19,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>69565</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>59089</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>84317</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>113242</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129629</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>125945</t>
+          <t>125416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142313</t>
+          <t>141969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>244626</t>
+          <t>243502</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>266497</t>
+          <t>266033</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25682</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>41257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>55517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76857</t>
+          <t>77832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174074</t>
+          <t>174399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190120</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165112</t>
+          <t>165069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182560</t>
+          <t>182323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344454</t>
+          <t>344041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367833</t>
+          <t>367735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,18%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>21180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>38364</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>41464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>561168</t>
+          <t>564245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>594746</t>
+          <t>595776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>601367</t>
+          <t>602335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>635723</t>
+          <t>635749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1175115</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1220500</t>
+          <t>1224153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102190</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134076</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105714</t>
+          <t>105517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>138030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216644</t>
+          <t>214536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>262404</t>
+          <t>260543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>89279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102476</t>
+          <t>102502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108582</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>127125</t>
+          <t>126769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203483</t>
+          <t>204414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225746</t>
+          <t>225873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54210</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135193</t>
+          <t>136332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162219</t>
+          <t>162556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210358</t>
+          <t>210916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>230175</t>
+          <t>230541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354381</t>
+          <t>354507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387804</t>
+          <t>387908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55319</t>
+          <t>54180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>44119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57744</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91167</t>
+          <t>91041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151483</t>
+          <t>151948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>173864</t>
+          <t>173102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>146912</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166353</t>
+          <t>165966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>306042</t>
+          <t>304510</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>334493</t>
+          <t>335200</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>16483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68829</t>
+          <t>70361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139199</t>
+          <t>140510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155220</t>
+          <t>155085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135781</t>
+          <t>135660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154646</t>
+          <t>154821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>281136</t>
+          <t>283145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307653</t>
+          <t>306832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45457</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>41645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>67341</t>
+          <t>65332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>540737</t>
+          <t>539979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>580162</t>
+          <t>580609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>623942</t>
+          <t>626659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>662328</t>
+          <t>662355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1175066</t>
+          <t>1174859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1230418</t>
+          <t>1232167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84455</t>
+          <t>84008</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123880</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99644</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196171</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251523</t>
+          <t>251730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
